--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\tickin-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EE7F62-C245-4C29-88A9-2A98E5C9D9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98917C7D-9FBD-4ED2-A913-C98D212400D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8F9EC6A3-5278-431F-A708-AD6595471329}"/>
   </bookViews>
@@ -87,18 +87,6 @@
     <t>MILK</t>
   </si>
   <si>
-    <t>200ML ALMOND BADAM MILK</t>
-  </si>
-  <si>
-    <t>200ML CHOCOBLAST</t>
-  </si>
-  <si>
-    <t>200ML ROSEMILK</t>
-  </si>
-  <si>
-    <t>200ML VENILLA</t>
-  </si>
-  <si>
     <t>FRUTANG</t>
   </si>
   <si>
@@ -124,6 +112,18 @@
   </si>
   <si>
     <t>Product Id</t>
+  </si>
+  <si>
+    <t>180ML ALMOND BADAM MILK</t>
+  </si>
+  <si>
+    <t>180ML CHOCOBLAST</t>
+  </si>
+  <si>
+    <t>180ML ROSEMILK</t>
+  </si>
+  <si>
+    <t>180ML VENILLA</t>
   </si>
 </sst>
 </file>
@@ -552,7 +552,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -680,7 +680,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C11" s="4">
         <v>1010</v>
@@ -692,7 +692,7 @@
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C12" s="4">
         <v>1011</v>
@@ -704,7 +704,7 @@
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C13" s="4">
         <v>1012</v>
@@ -716,7 +716,7 @@
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C14" s="4">
         <v>1013</v>
@@ -727,10 +727,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C15" s="4">
         <v>1014</v>
@@ -742,7 +742,7 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C16" s="4">
         <v>1015</v>
@@ -754,7 +754,7 @@
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C17" s="4">
         <v>1016</v>
@@ -765,10 +765,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C18" s="4">
         <v>1017</v>
@@ -780,7 +780,7 @@
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C19" s="4">
         <v>1018</v>
@@ -792,7 +792,7 @@
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C20" s="4">
         <v>1019</v>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\tickin-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98917C7D-9FBD-4ED2-A913-C98D212400D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0D534C-9DF1-4004-A75D-23ECCD0A37CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8F9EC6A3-5278-431F-A708-AD6595471329}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Category</t>
   </si>
@@ -124,13 +124,61 @@
   </si>
   <si>
     <t>180ML VENILLA</t>
+  </si>
+  <si>
+    <t>DIET</t>
+  </si>
+  <si>
+    <t>300ML DIET BOVONTO</t>
+  </si>
+  <si>
+    <t>300ML DIET VIBRO</t>
+  </si>
+  <si>
+    <t>PRE BIOTIC</t>
+  </si>
+  <si>
+    <t>250ML ACE PREBIOTIC SODA</t>
+  </si>
+  <si>
+    <t>250ML VENNILA PREBIOTIC SODA</t>
+  </si>
+  <si>
+    <t>12RS PACK</t>
+  </si>
+  <si>
+    <t>200ML MANGO</t>
+  </si>
+  <si>
+    <t>200ML OK</t>
+  </si>
+  <si>
+    <t>200ML ZIMZO</t>
+  </si>
+  <si>
+    <t>200ML TIGO</t>
+  </si>
+  <si>
+    <t>LASSI</t>
+  </si>
+  <si>
+    <t>180ML SWEET LASSI</t>
+  </si>
+  <si>
+    <t>180ML MANGO LASSI</t>
+  </si>
+  <si>
+    <t>180ML ROSE LASSI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.00_ "/>
+  </numFmts>
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,16 +215,70 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -199,11 +301,107 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -221,12 +419,286 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{E704B203-528F-40EE-9A0B-99E85D3F0181}"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{948752C5-90AF-4EA2-9D80-1B9392B490BB}">
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{EAC21DBF-F0F3-47EE-9213-11E14876CE65}">
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -535,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA31A4B1-0F37-42A5-B178-8A680BE8486E}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -801,8 +1273,152 @@
         <v>14.3</v>
       </c>
     </row>
+    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="14">
+        <v>1020</v>
+      </c>
+      <c r="D21" s="7">
+        <v>351.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="23"/>
+      <c r="B22" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="14">
+        <v>1021</v>
+      </c>
+      <c r="D22" s="7">
+        <v>351.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="11">
+        <v>1022</v>
+      </c>
+      <c r="D23" s="12">
+        <v>439.53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="25"/>
+      <c r="B24" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="11">
+        <v>1023</v>
+      </c>
+      <c r="D24" s="12">
+        <v>439.53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="14">
+        <v>1024</v>
+      </c>
+      <c r="D25" s="13">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="26"/>
+      <c r="B26" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="14">
+        <v>1025</v>
+      </c>
+      <c r="D26" s="13">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="26"/>
+      <c r="B27" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="14">
+        <v>1026</v>
+      </c>
+      <c r="D27" s="13">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="23"/>
+      <c r="B28" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="14">
+        <v>1027</v>
+      </c>
+      <c r="D28" s="13">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="9">
+        <v>1028</v>
+      </c>
+      <c r="D29" s="8">
+        <v>540.96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="20"/>
+      <c r="B30" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="11">
+        <v>1029</v>
+      </c>
+      <c r="D30" s="8">
+        <v>540.96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="21"/>
+      <c r="B31" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="10">
+        <v>1030</v>
+      </c>
+      <c r="D31" s="8">
+        <v>540.96</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="10">
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A25:A28"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A8:A9"/>
